--- a/Resources/TimeTable/ICT/ICT_timetable.xlsx
+++ b/Resources/TimeTable/ICT/ICT_timetable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test merge Project\Merge_project\Resources\TimeTable\ICT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supun\Documents\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEA11A59-AED7-42AD-92DB-95A2C84E92D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D3A8F3-57A5-4527-8BF0-CC68A71EB3C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{DF94511C-5F7E-4711-8284-BD98C03C5B2F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Monday</t>
   </si>
@@ -55,48 +55,12 @@
     <t>Friday</t>
   </si>
   <si>
-    <t>ICT1112</t>
-  </si>
-  <si>
     <t>12pm-1pm</t>
   </si>
   <si>
     <t>INTERVAL</t>
   </si>
   <si>
-    <t>ICT3122</t>
-  </si>
-  <si>
-    <t>ICT1132</t>
-  </si>
-  <si>
-    <t>ICT3112</t>
-  </si>
-  <si>
-    <t>ICT4132</t>
-  </si>
-  <si>
-    <t>ICT4121</t>
-  </si>
-  <si>
-    <t>ICT1152</t>
-  </si>
-  <si>
-    <t>ICT1122</t>
-  </si>
-  <si>
-    <t>ICT1162</t>
-  </si>
-  <si>
-    <t>ICT13132</t>
-  </si>
-  <si>
-    <t>ICT3143</t>
-  </si>
-  <si>
-    <t>ICT3151</t>
-  </si>
-  <si>
     <t>8am-9am</t>
   </si>
   <si>
@@ -121,38 +85,118 @@
     <t>11am-12pm</t>
   </si>
   <si>
-    <t>ICT415</t>
-  </si>
-  <si>
-    <t>ICT1142</t>
+    <t>ICT13132
+Rapid and Agile Software Development       
+Ms. Akila             
+ LAB 12</t>
+  </si>
+  <si>
+    <t>ICT1162
+Fundamentals of  Mathematics
+Ms. Sanjeewani
+LH 250</t>
+  </si>
+  <si>
+    <t>ICT3151
+IT Project Management 
+Ms. Shakila
+ (ILT)</t>
+  </si>
+  <si>
+    <t>ICT415
+Human Computer Interaction  
+Ms. Piyumi 
+LAB 12</t>
+  </si>
+  <si>
+    <t>ICT2133(P)
+Machine Learning
+Basics
+Mr.Chamara
+Gunasekara</t>
+  </si>
+  <si>
+    <t>ICT1152
+Computer Hardware
+Mrs.Supuni</t>
+  </si>
+  <si>
+    <t>ICT3143
+ IOT 
+Ms. Shalini
+ (ILT)</t>
+  </si>
+  <si>
+    <t>ICT2152
+CyberSecurity Essentials
+Mr.Jayalath Manorathna</t>
+  </si>
+  <si>
+    <t>ICT4121
+Artificial Intelligence           Ms. Malsha
+(ICT New Lab)</t>
+  </si>
+  <si>
+    <t>ICT4132
+Advance Programming
+Mr.Lakshitha Sandaruwan
+LAB 11</t>
+  </si>
+  <si>
+    <t>ICT1132
+Information System
+Mr.Samantha Priyankara
+LAB 11</t>
+  </si>
+  <si>
+    <t>ICT1112
+Fundemental Of Math
+Mr.Pushpa Kumara
+LH250</t>
+  </si>
+  <si>
+    <t>ICT1142
+Web Development
+Mr.Ganuka Chandralal
+NBLLT</t>
+  </si>
+  <si>
+    <t>ICT1112
+Fundemental Of ICT
+Mr.Shantha Kumara</t>
+  </si>
+  <si>
+    <t>ICT3122 
+Advanse Java
+Mr.Akila Disanayaka</t>
+  </si>
+  <si>
+    <t>ICT2122
+web Technologyes
+Mr.Sachini ekanayake</t>
+  </si>
+  <si>
+    <t>ICT1122
+Computer Network
+Ms.Kumudu Sandeepani
+LAB 12</t>
+  </si>
+  <si>
+    <t>ICT3112
+ python Programming
+Mr.Lakmal Ranaweera
+LAB 11</t>
   </si>
   <si>
     <t>ICT2133(T)
 Machine Learning
 Basics
-Chamara
-Gunasekara</t>
-  </si>
-  <si>
-    <t>ICT2122
-web Technologyes
-Sachini ekanayake</t>
+Mr.Chamara Gunasekara</t>
   </si>
   <si>
     <t>ICT2142
 Software Development
-Kumuduni Perera</t>
-  </si>
-  <si>
-    <t>ICT2133(T)
-Machine Learning
-Basics
-Chamara Gunasekara</t>
-  </si>
-  <si>
-    <t>ICT2152
-CyberSecurity Essentials
-Jayalath Manorathna</t>
+Ms.Kumuduni Perera</t>
   </si>
 </sst>
 </file>
@@ -196,7 +240,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -219,15 +263,177 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -235,6 +441,26 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -610,176 +836,187 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89D14C2-C1F7-4D62-8DB6-248648874CE2}">
-  <dimension ref="C5:I15"/>
+  <dimension ref="C5:I17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="G5" s="1"/>
-    </row>
+    <row r="5" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C7" s="2"/>
-      <c r="D7" s="3" t="s">
-        <v>19</v>
+      <c r="D7" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C8" s="2"/>
-      <c r="D8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="D8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C9" s="2"/>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
+      <c r="D9" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C10" s="2"/>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
+      <c r="D10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C11" s="2"/>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="3:9" ht="33" x14ac:dyDescent="0.3">
       <c r="C12" s="2"/>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="4" t="s">
+    </row>
+    <row r="13" spans="3:9" ht="33" x14ac:dyDescent="0.3">
+      <c r="C13" s="2"/>
+      <c r="D13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="2"/>
-      <c r="D13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
+      <c r="E13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C14" s="2"/>
-      <c r="D14" s="3" t="s">
-        <v>22</v>
+      <c r="D14" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="2"/>
-      <c r="D15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
+      <c r="D15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="16"/>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="E11:I11"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="H12:H15"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="E9:E10"/>
@@ -796,13 +1033,16 @@
     <mergeCell ref="I14:I15"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="G12:G13"/>
+    <mergeCell ref="E11:I11"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="H12:H15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="I9 G9 D10">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D9 H9">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I9 G9 D10">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
